--- a/data/trans_dic/P79_n_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79_n_R2-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,15</t>
+          <t>2,33; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,96</t>
+          <t>2,13; 4,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,0</t>
+          <t>2,53; 4,44</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,62</t>
+          <t>2,78; 5,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,82</t>
+          <t>3,51; 6,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,58</t>
+          <t>3,42; 5,2</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,34</t>
+          <t>2,41; 5,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,05</t>
+          <t>2,73; 5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,91</t>
+          <t>2,93; 5,13</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,88</t>
+          <t>3,76; 6,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,97</t>
+          <t>3,3; 5,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,9</t>
+          <t>3,79; 5,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,52</t>
+          <t>3,47; 5,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,2</t>
+          <t>3,5; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,17</t>
+          <t>3,64; 4,61</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>48452</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13398; 32713</t>
+          <t>16071; 37803</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12843; 28702</t>
+          <t>15666; 33434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29279; 54483</t>
+          <t>36074; 63315</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>48799</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77838</t>
+          <t>90055</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17859; 55051</t>
+          <t>29194; 57934</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31495; 55760</t>
+          <t>37625; 64452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49813; 98506</t>
+          <t>72548; 110291</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56291</t>
+          <t>61541</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18525; 44647</t>
+          <t>19326; 45169</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12442; 47106</t>
+          <t>22135; 46533</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37304; 80362</t>
+          <t>47315; 82932</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>49538</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40764</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81663</t>
+          <t>97828</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30308; 54486</t>
+          <t>37219; 66038</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29828; 54371</t>
+          <t>36873; 62942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64457; 99010</t>
+          <t>79845; 117452</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>130345</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>297877</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98439; 156452</t>
+          <t>122482; 177615</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102614; 155967</t>
+          <t>130758; 176427</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217030; 298878</t>
+          <t>264928; 335361</t>
         </is>
       </c>
     </row>
